--- a/tame_output/ON/bt/strategyON_20231016.xlsx
+++ b/tame_output/ON/bt/strategyON_20231016.xlsx
@@ -595,7 +595,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>42.6%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -605,7 +605,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -614,7 +614,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1748</v>
+        <v>1749</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2023-10-14</t>
+          <t>2023-10-15</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>68.2%</t>
+          <t>68.1%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -671,12 +671,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>19.0%</t>
+          <t>18.4%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.4%</t>
+          <t>-11.9%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -736,7 +736,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>57.0%</t>
+          <t>58.2%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>77.3%</t>
+          <t>77.4%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -758,7 +758,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1748</v>
+        <v>1749</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2023-10-14</t>
+          <t>2023-10-15</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>9.5%</t>
+          <t>9.9%</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>33.0%</t>
+          <t>32.9%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -920,7 +920,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1748</v>
+        <v>1749</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2023-10-14</t>
+          <t>2023-10-15</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>453.2%</t>
+          <t>453.4%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>13.8%</t>
+          <t>13.7%</t>
         </is>
       </c>
     </row>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>100.3%</t>
+          <t>100.4%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1073,7 +1073,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1748</v>
+        <v>1749</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2023-10-14</t>
+          <t>2023-10-15</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>15.0%</t>
+          <t>15.4%</t>
         </is>
       </c>
     </row>
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1748</v>
+        <v>1749</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2023-10-14</t>
+          <t>2023-10-15</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1360,7 +1360,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>130.0%</t>
+          <t>130.1%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1379,7 +1379,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1748</v>
+        <v>1749</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2023-10-14</t>
+          <t>2023-10-15</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>124.6%</t>
+          <t>124.7%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-14.5%</t>
+          <t>-14.6%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>14.0%</t>
         </is>
       </c>
     </row>
@@ -1516,7 +1516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1751"/>
+  <dimension ref="A1:G1752"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41783,7 +41783,7 @@
         <v>45213</v>
       </c>
       <c r="B1751" t="n">
-        <v>2.805336308940817</v>
+        <v>2.804617428641442</v>
       </c>
       <c r="C1751" t="n">
         <v>2.950191610492619</v>
@@ -41799,6 +41799,29 @@
       </c>
       <c r="G1751" t="n">
         <v>4.24713776158009</v>
+      </c>
+    </row>
+    <row r="1752">
+      <c r="A1752" s="2" t="n">
+        <v>45214</v>
+      </c>
+      <c r="B1752" t="n">
+        <v>2.817300619330886</v>
+      </c>
+      <c r="C1752" t="n">
+        <v>2.953840430523644</v>
+      </c>
+      <c r="D1752" t="n">
+        <v>1.561659974925487</v>
+      </c>
+      <c r="E1752" t="n">
+        <v>3.578147996180092</v>
+      </c>
+      <c r="F1752" t="n">
+        <v>2.161576918479115</v>
+      </c>
+      <c r="G1752" t="n">
+        <v>4.250786581611115</v>
       </c>
     </row>
   </sheetData>
